--- a/tests/fixtures/import/event-patterns/Marigold's Harvest Supper.xlsx
+++ b/tests/fixtures/import/event-patterns/Marigold's Harvest Supper.xlsx
@@ -716,7 +716,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1 Medical Gluten</v>
+        <v>1 Celiac Diet</v>
       </c>
       <c r="B25" t="str">
         <v/>
